--- a/src/test/resources/testdata.xlsx
+++ b/src/test/resources/testdata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cognizantonline-my.sharepoint.com/personal/2484058_cognizant_com/Documents/Desktop/Mini_Projects/EMICalculator/src/test/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="400" documentId="11_F25DC773A252ABDACC104836919C744E5ADE5903" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{888E7155-9725-418C-9188-1C264667E6B2}"/>
+  <xr:revisionPtr revIDLastSave="412" documentId="11_F25DC773A252ABDACC104836919C744E5ADE5903" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A9B0BAB7-CB99-41B6-9A44-D3DBEA2CB137}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -76,7 +76,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -99,16 +99,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFE6E6E6"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFE6E6E6"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -391,7 +405,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.6328125" customWidth="1"/>
@@ -512,6 +526,50 @@
         <v>360</v>
       </c>
     </row>
+    <row r="11" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="3">
+        <v>400000</v>
+      </c>
+      <c r="B11" s="3">
+        <v>10</v>
+      </c>
+      <c r="C11" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="3">
+        <v>1000000</v>
+      </c>
+      <c r="B12" s="3">
+        <v>10</v>
+      </c>
+      <c r="C12" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="3">
+        <v>3000000</v>
+      </c>
+      <c r="B13" s="3">
+        <v>10</v>
+      </c>
+      <c r="C13" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="3">
+        <v>800</v>
+      </c>
+      <c r="B14" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C14" s="3">
+        <v>367</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
